--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMExamenImagerie vers le profil CDA FRCDADICOMExamenImagerie, puis vers le profil FHIR FRImagingStudyDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMImagingStudy vers le profil CDA FRCDADICOMExamenImagerie, puis vers le profil FHIR FRImagingStudyDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-examen-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-imaging-study</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-examen-imagerie</t>
   </si>
   <si>
-    <t>FRLMExamenImagerie</t>
+    <t>FRLMImagingStudy</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,40 +118,34 @@
     <t>FRCDADICOMExamenImagerie</t>
   </si>
   <si>
-    <t>FRLMExamenImagerie.uuidInstanceExamen</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.id</t>
-  </si>
-  <si>
-    <t>FRLMExamenImagerie.codeActe</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.code</t>
-  </si>
-  <si>
-    <t>FRLMExamenImagerie.description</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.text</t>
-  </si>
-  <si>
-    <t>FRLMExamenImagerie.dateActe</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMExamenImagerie.serieImagerie</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.entryRelationship:frDICOMSerieImagerie</t>
-  </si>
-  <si>
-    <t>FRLMExamenImagerie.objectifsReferences</t>
-  </si>
-  <si>
-    <t>FRCDADICOMExamenImagerie.entryRelationship:frDICOMSerieImagerie.entryRelationship:frDICOMSOPInstanceObservation.entryRelationship:frDICOMObjectifsDeReference</t>
+    <t>FRLMImagingStudy.header.identifier</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.id</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.modality</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.methodCode</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.targetSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.bodySite:FRLMBodyStructure.locationQualifier</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.targetSiteCode.qualifier</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.started</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.effectiveTime</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-imaging-study-document</t>
@@ -160,19 +154,58 @@
     <t>FRImagingStudyDocument</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.identifier:studyInstanceUid</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.description</t>
+    <t>FRImagingStudyDocument.identifier</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.modality</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.bodySite</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.encounter</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.encounter</t>
   </si>
   <si>
     <t>FRImagingStudyDocument.started</t>
   </si>
   <si>
+    <t>FRLMImagingStudy.basedOn</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.basedOn</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.numberOfSeries</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.numberOfSeries</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.numberOfInstances</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.numberOfInstances</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.studyCustodian</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.series.performer.actor:Organization</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.studyEndpoint</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument.endpoint</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.series</t>
+  </si>
+  <si>
     <t>FRImagingStudyDocument.series</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.reasonCode</t>
   </si>
 </sst>
 </file>
@@ -424,7 +457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -538,19 +571,6 @@
         <v>43</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -559,7 +579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -581,7 +601,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -590,7 +610,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -598,81 +618,159 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-imaging-study</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-imaging-study|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-examen-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-examen-imagerie|0.1.0</t>
   </si>
   <si>
     <t>FRLMImagingStudy</t>
@@ -148,7 +148,7 @@
     <t>FRCDADICOMTechniqueImagerie.effectiveTime</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-imaging-study-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0</t>
   </si>
   <si>
     <t>FRImagingStudyDocument</t>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRImagingStudyLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-imaging-study|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMImagingStudy|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,97 +121,94 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Act</t>
+  </si>
+  <si>
     <t>FRCDADICOMExamenImagerie</t>
   </si>
   <si>
     <t>FRLMImagingStudy.header.identifier</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.id</t>
+    <t>Act.id</t>
   </si>
   <si>
     <t>FRLMImagingStudy.modality</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.methodCode</t>
+    <t>Act.code.qualifier</t>
+  </si>
+  <si>
+    <t>FRLMImagingStudy.started</t>
+  </si>
+  <si>
+    <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0</t>
+  </si>
+  <si>
+    <t>ImagingStudy</t>
+  </si>
+  <si>
+    <t>FRImagingStudyDocument</t>
+  </si>
+  <si>
+    <t>ImagingStudy.identifier</t>
+  </si>
+  <si>
+    <t>ImagingStudy.modality</t>
   </si>
   <si>
     <t>FRLMImagingStudy.bodySite</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMImagingStudy.bodySite:FRLMBodyStructure.locationQualifier</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.targetSiteCode.qualifier</t>
-  </si>
-  <si>
-    <t>FRLMImagingStudy.started</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.effectiveTime</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.modality</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.bodySite</t>
+    <t>ImagingStudy.series.bodySite</t>
   </si>
   <si>
     <t>FRLMImagingStudy.encounter</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.encounter</t>
-  </si>
-  <si>
-    <t>FRImagingStudyDocument.started</t>
+    <t>ImagingStudy.encounter</t>
+  </si>
+  <si>
+    <t>ImagingStudy.started</t>
   </si>
   <si>
     <t>FRLMImagingStudy.basedOn</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.basedOn</t>
+    <t>ImagingStudy.basedOn</t>
   </si>
   <si>
     <t>FRLMImagingStudy.numberOfSeries</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.numberOfSeries</t>
+    <t>ImagingStudy.numberOfSeries</t>
   </si>
   <si>
     <t>FRLMImagingStudy.numberOfInstances</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.numberOfInstances</t>
+    <t>ImagingStudy.numberOfInstances</t>
   </si>
   <si>
     <t>FRLMImagingStudy.studyCustodian</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.series.performer.actor:Organization</t>
+    <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
     <t>FRLMImagingStudy.studyEndpoint</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.endpoint</t>
+    <t>ImagingStudy.endpoint</t>
   </si>
   <si>
     <t>FRLMImagingStudy.series</t>
   </si>
   <si>
-    <t>FRImagingStudyDocument.series</t>
+    <t>ImagingStudy.series</t>
   </si>
 </sst>
 </file>
@@ -374,79 +377,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -457,120 +464,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -584,58 +567,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>46</v>
@@ -644,11 +629,11 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>47</v>
@@ -657,118 +642,118 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="2"/>
     </row>

--- a/main/ig/FRImagingStudyLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingStudyLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
